--- a/docs/perechen-otchetov/obrazcy/ФО-16.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-16.xlsx
@@ -7,18 +7,27 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Образец" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ФО-16" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вид 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вид 1 — параметры" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ФО-16'!$5:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Вид 1'!$5:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  </numFmts>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +36,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -50,12 +91,37 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D08E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -89,59 +155,139 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,312 +653,463 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="7.8" customWidth="1" min="9" max="9"/>
+    <col width="7.8" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Информация по снятию с ареста (запрета на отчуждение)</t>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-16</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>за период с 01.09.2026 по 30.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Кол-во заёмщиков</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Кол-во снятий</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Снятие запрета на отчуждение</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>за период с 01.09.2026 по 30.09.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Вид залога</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Договор залога</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Обеспечивал кредиты</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Запрет на отчуждение</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Дата снятия</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Вид снятия</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Основание снятия</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Предметов</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Снятий</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Оценочная стоимость</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Залоговая стоимость</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Снятие с ареста</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Вид снятия</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Основание</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="6" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="J8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Ошская область</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="6" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="K8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>г. Ош</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="J9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="K9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>г. Ош</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="10" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="J10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="K10" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>ОсОО «Ош-Нан»</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="10" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr"/>
-      <c r="B10" s="7" t="n">
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Договор залога № 20-1/412-З1 от 14.10.2020</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="K11" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="24" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M11" s="24" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Торговое помещение</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Недвижимое имущество</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>№ 20-1/412-З1 от 14.10.2020</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>№ 20-1/412 от 14.10.2020</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="7" t="n">
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>нотариальная контора г. Ош, № ЗПО-20/0314 от 20.10.2020</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Торговое помещение</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="10" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F11" s="9" t="inlineStr"/>
-      <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="7" t="n">
+      <c r="L12" s="24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="13" ht="35" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Реестровая запись нотариуса о снятии запрета № 2-1412 от 22.09.2026</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="28" t="n">
+        <v>46287</v>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>полное</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>полное погашение обязательства; акт сверки № 12-04/1204 от 18.09.2026</t>
+        </is>
+      </c>
+      <c r="I13" s="29" t="n"/>
+      <c r="J13" s="29" t="n"/>
+      <c r="K13" s="29" t="n"/>
+      <c r="L13" s="30" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="14" ht="35" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Хлебопекарная линия</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>№ 20-1/412-З1 от 14.10.2020</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>№ 20-1/412 от 14.10.2020</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>реестр залогов движимого имущества, № РЗД-20/04412 от 16.10.2020</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="L14" s="24" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M14" s="24" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" ht="35" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Запись о прекращении залога в реестре движимого имущества № РЗД-26/08841 от 24.09.2026</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="28" t="n">
+        <v>46289</v>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>полное</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Полное погашение кредита</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Акт сверки о полном погашении от 18.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr"/>
-      <c r="B13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Хлебопекарное оборудование</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="10" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="F13" s="9" t="inlineStr"/>
-      <c r="G13" s="9" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr"/>
-      <c r="I13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr"/>
-      <c r="B14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr"/>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>полное</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>Полное погашение кредита</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Акт сверки о полном погашении от 18.09.2026</t>
-        </is>
+      <c r="H15" s="27" t="inlineStr">
+        <is>
+          <t>полное погашение обязательства; акт сверки № 12-04/1204 от 18.09.2026</t>
+        </is>
+      </c>
+      <c r="I15" s="29" t="n"/>
+      <c r="J15" s="29" t="n"/>
+      <c r="K15" s="29" t="n"/>
+      <c r="L15" s="30" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A1:I1"/>
+  <mergeCells count="15">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-16 · сформировал Осмонов Б. Т. 06.10.2026 10:40 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -822,7 +1119,626 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>ФО-16 «Снятие запрета на отчуждение за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>01.09.2026 – 30.09.2026 (по умолчанию — прошлый месяц)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>Область → Район → Заёмщик → Предмет залога → снятие</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Реквизиты разрезов</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>на дату снятия</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="39" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Стоимость</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>только у полного снятия, на дату снятия: оценочная — по последней оценке не позже даты; залоговая — оценочная × коэффициент вида с учётом понижения, действовавшего на ту же дату; всё в сомах</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Период закрыт</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>06.10.2026 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>Осмонов Б. Т.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="7.8" customWidth="1" min="8" max="8"/>
+    <col width="7.8" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Запреты, подлежащие снятию</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>по состоянию на 01.10.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Вид залога</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Договор залога</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Обеспечивал кредиты</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Запрет на отчуждение</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Основание снятия</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Подлежит снятию с</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Предметов</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Оценочная стоимость</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Залоговая стоимость</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Дней ожидания</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L8" s="34" t="n"/>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>Неполучение кредитных средств</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="38" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K9" s="38" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L9" s="39" t="n"/>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>КФХ «Береке»</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="35" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>Животноводческое помещение с земельным участком</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Недвижимое имущество</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>№ 26-1/012-З1 от 14.07.2026</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>№ 26-1/012 от 14.07.2026</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>нотариальная контора Ат-Башинского района, № ЗПО-26/0117 от 17.07.2026</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>неполучение кредитных средств; соглашение о расторжении № 5 от 10.09.2026</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>46275</v>
+      </c>
+      <c r="H11" s="29" t="n"/>
+      <c r="I11" s="29" t="n"/>
+      <c r="J11" s="30" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L11" s="42" t="n">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C5:C6"/>
+  </mergeCells>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-16 · сформировал Осмонов Б. Т. 01.10.2026 09:55 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>ФО-16 «Запреты, подлежащие снятию, по состоянию на дату» — вид отчёта «Снятие запрета на отчуждение за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Дата состояния</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>01.10.2026 (данные на конец 30.09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>Основание снятия → Заёмщик → предмет</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Стоимость</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>на дату: оценочная — по последней оценке не позже даты; залоговая — оценочная × коэффициент вида с учётом понижения, действовавшего на ту же дату; всё в сомах</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>01.10.2026 02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Осмонов Б. Т.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -831,416 +1747,708 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>ФО-16 «Снятие с ареста (запрета на отчуждение)» — карточка</t>
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>ФО-16 «Снятие запрета на отчуждение за период» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>ФО-16</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>Снятие запрета на отчуждение за период</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>Залог</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
         <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="44" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Порядок №41 пп. 10, 64; Положение №12 п. 7.2, прил. 3; ТЗ 12; старая система</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="165" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Отделу залогового обеспечения — контролировать, что после погашения кредита запрет на отчуждение предметов залога снят и об этом есть запись: когда, какой вид снятия и по какому основанию.</t>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>Отделу залогового обеспечения Департамента администрирования кредитов, кураторам Департамента администрирования кредитов и Департамента регионального развития, руководству Холдинга — с каких предметов залога за период снят запрет на отчуждение: когда, полностью или с части предмета, по какому основанию и каким документом органа, сколько снятий и на какую стоимость. Проект снятия готовит отдел залогового обеспечения, согласует с отраслевым департаментом и отделом правовой экспертизы, подписывает курирующий заместитель Председателя Правления (Положение №12 прил. 3). Где запрет ещё не снят, хотя оснований держать его нет, — вид «Запреты, подлежащие снятию, по состоянию на дату»; предметы в залоге на дату с состоянием запрета — ФО-14; погашенные кредиты — ФО-95; извещение нотариусу или регистрирующему органу — бланк ФО-90. Прежнее название — «Снятие с ареста (запрета на отчуждение)»; в старой системе — «Отчет по снятию с ареста» («Информация по снятию с ареста»).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>За период (по умолчанию — прошлый месяц); по требованию, в том числе после массового погашения кредитов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="105" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>За период: ежемесячно и по требованию, в том числе после массового погашения кредитов; по умолчанию — прошлый месяц. Можно выбрать любой период (за год — с 1 января).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>• Период снятия — с первого по последнее число прошлого месяца
-• Область, район, отрасль, заёмщик — все
-• Вид снятия — все (полное, частичное)
-• Основание снятия — все
-• Единица — сом; можно выбрать тыс. сом</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>• Период — прошлый месяц; можно выбрать любой
+• Единица — тыс. сом (можно выбрать «сом»)
+• Разрезы — до шести уровней в любом порядке; по умолчанию область → район → заёмщик → предмет залога → снятие. Доступны: департамент, отдел, куратор, область, район, отрасль, вид залога, вид снятия, основание снятия, месяц, заёмщик, договор залога, предмет залога
+• Отбор — по любому из разрезов; вид снятия и основание снятия — несколько значений</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="330" customHeight="1">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Область → район → заёмщик → договор залога → предмет залога → снятие. Подытоги на каждом уровне выше снятия, сверху ИТОГО. Снятия предмета — по возрастанию даты. Предмет, с которого запрет не снимался в периоде, в отчёт не попадает.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Строка детали — снятие запрета на отчуждение с предмета залога: полное — с предмета целиком, частичное — с части предмета, запрет на остаток сохраняется. В отчёт попадают действующие записи о снятии с датой снятия в периоде, в том числе снятия, перенесённые из прежней системы. Не попадают: сторнированная запись (вместо неё — исправленная, если она есть); согласие на действия с предметом без снятия запрета — запрет при нём остаётся; прекращение поручительства — у него нет запрета. Над снятиями — разрезы, по умолчанию область → район → заёмщик → предмет залога; область и район — заёмщика; у городов республиканского значения — обе строки, области и района. Строка предмета есть всегда, даже при одном снятии: в ней вид залога, договор залога, кредиты, которые он обеспечивал, снятый запрет (орган, номер и дата наложения), число снятий и их стоимость; у залогодателя — третьего лица после названия «залогодатель — &lt;наименование&gt;». Строка снятия — документ органа о снятии («реестровая запись … № … от …»): дата снятия, вид, основание. Основание — по классификатору оснований снятия; при полном погашении — с актом сверки о полном погашении. Стоимость — только у полного снятия: оценочная по последней оценке предмета не позже даты снятия и залоговая = оценочная × коэффициент вида с учётом понижения на ту же дату; у частичного пусто — стоимость снятой части не записывается. Предмет, заложенный по нескольким договорам, — одной строкой: запрет на предмет один, договоры перечислены в колонке; при разрезе «Договор залога» он — под самым ранним договором. Реквизиты разрезов (департамент, отдел, куратор) — на дату снятия. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками; строка заёмщика есть всегда. Порядок: области — по справочнику, районы — по алфавиту; заёмщики — по алфавиту наименования без организационной формы; предметы — по дате и номеру договора залога, затем по порядку в описи; снятия предмета — по дате. Суммы — в тыс. сом; стоимость залога всегда в сомах. Печать — A4 альбомная.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>по умолчанию: Область → Район → Заёмщик → Предмет залога → снятие запрета; можно выбрать: Департамент, Отдел, Куратор, Область, Район, Отрасль, Вид залога, Вид снятия, Основание снятия, Месяц, Заёмщик, Договор залога, Предмет залога</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>Если строк нет</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Снятий запрета на отчуждение за период по условиям отбора нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>Выгрузка</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>xlsx, pdf</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Снятие с ареста (запрета на отчуждение)»; в старой системе — «Отчет по снятию с ареста» («Информация по снятию с ареста»). Извещение о снятии — бланк ФО-90. Запреты, подлежащие снятию, на дату — вид отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>Общая шапка</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>Что в ней</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Кол-во заёмщиков</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr"/>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>число заёмщиков под строкой</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Кол-во снятий</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>число снятий запрета под строкой; в строке снятия — 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr"/>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>область, район, заёмщик, «Договор залога № … от …» или наименование предмета — по уровню строки</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr"/>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>номер и дата кредитного договора; выводится в строке договора залога</t>
+      <c r="B22" s="45" t="inlineStr"/>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>область, район, заёмщик, предмет залога или документ о снятии запрета («реестровая запись … № … от …») — по уровню строки; у предмета залогодателя — третьего лица после названия «залогодатель — &lt;наименование&gt;»</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Вид залога</t>
+        </is>
+      </c>
+      <c r="B23" s="45" t="inlineStr"/>
+      <c r="C23" s="45" t="inlineStr">
+        <is>
+          <t>вид из справочника видов залога; заполняется у предмета</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>Договор залога</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="inlineStr"/>
+      <c r="C24" s="45" t="inlineStr">
+        <is>
+          <t>«№ … от …» договора залога, по которому на предмет был наложен запрет; несколько — через запятую; заполняется у предмета</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t>Обеспечивал кредиты</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="inlineStr"/>
+      <c r="C25" s="45" t="inlineStr">
+        <is>
+          <t>«№ … от …» кредитов, к которым предмет был отнесён по этим договорам до освобождения долей; заполняется у предмета</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>Запрет на отчуждение</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="inlineStr"/>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>снятый запрет: орган, в котором он зарегистрирован (нотариальная контора или регистрирующий орган по виду имущества), номер и дата наложения; заполняется у предмета</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>Дата снятия</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="inlineStr"/>
+      <c r="C27" s="45" t="inlineStr">
+        <is>
+          <t>дата снятия запрета в органе — по документу о снятии; заполняется у снятия</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t>Вид снятия</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="inlineStr"/>
+      <c r="C28" s="45" t="inlineStr">
+        <is>
+          <t>«полное» — запрет снят с предмета целиком; «частичное: &lt;часть предмета&gt;» — снят с части, на остаток запрет сохраняется; заполняется у снятия</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>Основание снятия</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="inlineStr"/>
+      <c r="C29" s="45" t="inlineStr">
+        <is>
+          <t>основание по классификатору оснований снятия: полное погашение обязательства; решение Кабинета Министров о списании задолженности; недействительность основного обязательства или договора по решению суда; виндикация; замена залога (утрата, повреждение или по заявлению залогодателя); перевод долга с передачей предмета новому заёмщику; продажа с публичных торгов; переоформление на Холдинг нереализованного на торгах, отступное; частичное погашение при достаточном обеспечении; неполучение кредитных средств; отказ заёмщика от кредита; у частичного снятия — продажа части предмета по решению суда; продажа части по решению специального администратора; передача части предмета Холдингу в счёт погашения; иное при достаточном ликвидном остатке. При полном погашении через «;» — акт сверки о полном погашении, его номер и дата. У снятия, перенесённого из прежней системы, — её текст основания; заполняется у снятия</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="B30" s="45" t="inlineStr"/>
+      <c r="C30" s="45" t="inlineStr">
+        <is>
+          <t>число заёмщиков в разрезе; у заёмщика и ниже пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="inlineStr">
+        <is>
+          <t>Предметов</t>
+        </is>
+      </c>
+      <c r="B31" s="45" t="inlineStr"/>
+      <c r="C31" s="45" t="inlineStr">
+        <is>
+          <t>число предметов, с которых в периоде снят запрет полностью или частично, каждый один раз; у предмета и снятия пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>Снятий</t>
+        </is>
+      </c>
+      <c r="B32" s="45" t="inlineStr"/>
+      <c r="C32" s="45" t="inlineStr">
+        <is>
+          <t>число снятий за период — полных и частичных; у снятия пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="inlineStr">
+        <is>
+          <t>Оценочная стоимость</t>
+        </is>
+      </c>
+      <c r="B33" s="45" t="inlineStr"/>
+      <c r="C33" s="45" t="inlineStr">
+        <is>
+          <t>у полного снятия — оценочная стоимость предмета по последней оценке не позже даты снятия; у частичного пусто: стоимость снятой части не записывается; у предмета и разрезов — сумма снятий</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t>Залоговая стоимость</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>залоговая стоимость предмета на дату снятия, в сомах; в подытогах — сумма по предметам</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>Снятие с ареста</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>дата снятия запрета на отчуждение</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>Вид снятия</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Снятие с ареста</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>полное или частичное (оф. ТЗ ¶523); частичное — при частичном погашении долга и достаточном обеспечении (Положение №12 п. 7.2 пп. 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="B34" s="45" t="inlineStr"/>
+      <c r="C34" s="45" t="inlineStr">
+        <is>
+          <t>у полного снятия — оценочная × коэффициент вида с учётом понижения, действовавшего на дату снятия; у частичного пусто; у предмета и разрезов — сумма снятий</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="46" t="inlineStr">
+        <is>
+          <t>Правила проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B37" s="45" t="inlineStr">
+        <is>
+          <t>За сентябрь 2026: 1 заёмщик, 2 предмета, 2 снятия; оценочная стоимость 6 000,000, залоговая 3 800,000 тыс. сом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="75" customHeight="1">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B38" s="45" t="inlineStr">
+        <is>
+          <t>КЗ-15 ОсОО «Ош-Нан», кредит № 20-1/412 погашен 18.09.2026 (ФО-95), договор залога № 20-1/412-З1: торговое помещение — запрет нотариальной конторы г. Ош № ЗПО-20/0314 снят 22.09.2026 по извещению от 21.09.2026 (ФО-90); хлебопекарная линия — запрет в реестре залогов движимого имущества № РЗД-20/04412 снят 24.09.2026. Оба снятия — «полное», основание «полное погашение обязательства; акт сверки № 12-04/1204 от 18.09.2026» (ФО-34).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="44" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B39" s="45" t="inlineStr">
+        <is>
+          <t>Стоимость — по оценке 05.10.2020: торговое помещение 4 000,000 / 2 800,000 (недвижимость × 0,7), хлебопекарная линия 2 000,000 / 1 000,000 (оборудование × 0,5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B40" s="45" t="inlineStr">
+        <is>
+          <t>Число снятий в ИТОГО = числу действующих записей о снятии запрета в журналах предметов набора с датой снятия в периоде; сторнированная запись и согласие на действия без снятия запрета не входят.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="44" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B41" s="45" t="inlineStr">
+        <is>
+          <t>КЗ-18 КФХ «Береке» (кредит расторгнут 10.09.2026, средства не получены): запрет на 30.09.2026 не снят — в основном отчёте его нет, он в виде «Запреты, подлежащие снятию, по состоянию на дату».</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="44" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B42" s="45" t="inlineStr">
+        <is>
+          <t>Предметов КЗ-15 и КЗ-18 в ФО-14 на 01.10.2026 нет: доли под кредитами освобождены, статус залога «свободен».</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="44" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B43" s="45" t="inlineStr">
+        <is>
+          <t>Строка разреза = сумма строк на уровень ниже по счётчикам и суммам; стоимость предмета = сумме его полных снятий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="44" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B44" s="45" t="inlineStr">
+        <is>
+          <t>При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="46" t="inlineStr">
+        <is>
+          <t>Вид 1: «Запреты, подлежащие снятию, по состоянию на дату» — лист «Вид 1»</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="120" customHeight="1">
+      <c r="A47" s="44" t="inlineStr">
+        <is>
+          <t>Кому и зачем</t>
+        </is>
+      </c>
+      <c r="B47" s="45" t="inlineStr">
+        <is>
+          <t>Отделу залогового обеспечения Департамента администрирования кредитов, кураторам, руководству Холдинга — на каких предметах запрет на отчуждение действует без основания: кредиты, которые предмет обеспечивал, закрыты (погашены, списаны, расторгнуты) или предмет выведен из договора, реализован, а запрет не снят; с какого дня запрет подлежит снятию и сколько дней ждёт. Имущество залогодателя всё это время заблокировано без правового основания. В очереди «Мониторинг обеспечения» это видно по одному предмету («Требуется снятие запрета»); здесь — списком на дату. Снятые запреты за период — основной отчёт ФО-16; извещение нотариусу или регистрирующему органу — бланк ФО-90.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="44" t="inlineStr">
+        <is>
+          <t>Когда</t>
+        </is>
+      </c>
+      <c r="B48" s="45" t="inlineStr">
+        <is>
+          <t>По состоянию на дату, по требованию и после закрытия кредитов; по умолчанию — сегодня (данные на конец предыдущего дня). Можно выбрать любую дату.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="120" customHeight="1">
+      <c r="A49" s="44" t="inlineStr">
+        <is>
+          <t>Параметры</t>
+        </is>
+      </c>
+      <c r="B49" s="45" t="inlineStr">
+        <is>
+          <t>• Дата — сегодня (данные на конец предыдущего дня); можно выбрать любую
+• Единица — тыс. сом (можно выбрать «сом»)
+• Разрезы — до шести уровней в любом порядке; по умолчанию основание снятия → заёмщик → предмет. Доступны: основание снятия, департамент, отдел, куратор, область, район, отрасль, вид залога, заёмщик, договор залога
+• Отбор — по любому из разрезов; ждут снятия больше выбранного числа дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="225" customHeight="1">
+      <c r="A50" s="44" t="inlineStr">
+        <is>
+          <t>Строки</t>
+        </is>
+      </c>
+      <c r="B50" s="45" t="inlineStr">
+        <is>
+          <t>Строка детали — предмет, на котором на дату действует запрет на отчуждение, а долей под действующими кредитами нет: состояние запрета «подлежит снятию». Не попадают: предмет, который обеспечивает ещё хотя бы один действующий кредит, — доли живы, снимать запрет нельзя; предмет, с которого запрет снят до конца дня, — он в основном отчёте; предмет с запретом «не наложен» или «просрочен» — это залог без запрета, ФО-14; частично снятый запрет, пока предмет в залоге. Основание снятия — событие, после которого не осталось долей, по классификатору оснований, с документом; «подлежит снятию с» — дата этого события; дней ожидания = день, на конец которого взяты данные, − «подлежит снятию с». Над предметами — разрезы, по умолчанию основание снятия → заёмщик; строка заёмщика есть всегда, даже при одном предмете; у залогодателя — третьего лица после названия предмета «залогодатель — &lt;наименование&gt;». Первая строка — ИТОГО; строка разреза несёт число заёмщиков, предметов и стоимость; дни в строках разрезов пусты. Порядок: основания — по классификатору оснований снятия, пустые не показываются; внутри — заёмщики по наибольшему числу дней ожидания своих предметов, дольше ждущие сверху; предметы — по дням ожидания от большего, при равных — по дате и номеру договора и описи. Стоимость — на дату, как в ФО-14, в тыс. сом. Печать — A4 альбомная.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B51" s="45" t="inlineStr">
+        <is>
+          <t>по умолчанию: Основание снятия → Заёмщик → предмет залога; можно выбрать: Основание снятия, Департамент, Отдел, Куратор, Область, Район, Отрасль, Вид залога, Заёмщик, Договор залога</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="44" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>Снятие с ареста</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>основание снятия из классификатора оснований по Положению №12 п. 7.2: полное погашение задолженности; решение Кабинета Министров о списании; замена предмета залога; перевод долга; продажа с публичных торгов; частичное погашение долга и др.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>Снятие с ареста</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>документ-основание, номер и дата, комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Правила проверки</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>«Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Все даты снятия попадают в период отчёта.</t>
+      <c r="B52" s="45" t="inlineStr">
+        <is>
+          <t>Положение №12 п. 7.2, прил. 3; ТЗ 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="44" t="inlineStr">
+        <is>
+          <t>Образец-основа</t>
+        </is>
+      </c>
+      <c r="B53" s="45" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="44" t="inlineStr">
+        <is>
+          <t>Колонки</t>
+        </is>
+      </c>
+      <c r="B54" s="45" t="inlineStr">
+        <is>
+          <t>Наименование; Вид залога; Договор залога; Обеспечивал кредиты; Запрет на отчуждение; Основание снятия; Подлежит снятию с; Заёмщиков; Предметов; Оценочная стоимость; Залоговая стоимость; Дней ожидания</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>Проверка 1</t>
+        </is>
+      </c>
+      <c r="B55" s="45" t="inlineStr">
+        <is>
+          <t>На 01.10.2026: 1 заёмщик, 1 предмет; оценочная стоимость 1 800,000, залоговая 1 260,000 тыс. сом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1">
+      <c r="A56" s="44" t="inlineStr">
+        <is>
+          <t>Проверка 2</t>
+        </is>
+      </c>
+      <c r="B56" s="45" t="inlineStr">
+        <is>
+          <t>КЗ-18 КФХ «Береке»: кредит № 26-1/012 расторгнут 10.09.2026 соглашением № 5 без выдачи средств (ФО-58, ФО-84); животноводческое помещение с земельным участком по договору залога № 26-1/012-З1, запрет нотариальной конторы Ат-Башинского района № ЗПО-26/0117 от 17.07.2026 не снят — «неполучение кредитных средств», подлежит снятию с 10.09.2026, дней ожидания 20 (30.09.2026 − 10.09.2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="44" t="inlineStr">
+        <is>
+          <t>Проверка 3</t>
+        </is>
+      </c>
+      <c r="B57" s="45" t="inlineStr">
+        <is>
+          <t>КЗ-15 в виде нет: оба запрета сняты 22.09.2026 и 24.09.2026 — они в основном отчёте за сентябрь. На 21.09.2026 оба предмета КЗ-15 — в виде, «полное погашение обязательства», подлежат снятию с 18.09.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="44" t="inlineStr">
+        <is>
+          <t>Проверка 4</t>
+        </is>
+      </c>
+      <c r="B58" s="45" t="inlineStr">
+        <is>
+          <t>КЗ-04 и КЗ-14 в виде нет: предметы обеспечивают действующие кредиты; утраченный трактор КЗ-14 остаётся в договоре до восполнения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="44" t="inlineStr">
+        <is>
+          <t>Проверка 5</t>
+        </is>
+      </c>
+      <c r="B59" s="45" t="inlineStr">
+        <is>
+          <t>Строка разреза = сумма строк на уровень ниже по предметам и стоимости.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="37">
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
